--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$108</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3444" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3413" uniqueCount="357">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -783,7 +783,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t xml:space="preserve">profile:observation}
 </t>
   </si>
   <si>
@@ -992,12 +992,6 @@
   </si>
   <si>
     <t>Entry.supply</t>
-  </si>
-  <si>
-    <t>Section.entry:frTransfertDuPatient</t>
-  </si>
-  <si>
-    <t>frTransfertDuPatient</t>
   </si>
   <si>
     <t>Section.entry:frProbleme</t>
@@ -1443,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK109"/>
+  <dimension ref="A1:AK108"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="60.33984375" customWidth="true" bestFit="true"/>
@@ -9128,20 +9122,20 @@
         <v>317</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C76" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>75</v>
@@ -9153,10 +9147,12 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+      <c r="M76" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -9182,13 +9178,11 @@
         <v>75</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -9206,13 +9200,13 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>246</v>
+        <v>90</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>75</v>
@@ -9226,23 +9220,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E77" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>75</v>
@@ -9254,11 +9246,11 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9285,11 +9277,13 @@
         <v>75</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
@@ -9307,13 +9301,13 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>75</v>
@@ -9327,10 +9321,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9341,7 +9335,7 @@
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>75</v>
@@ -9353,11 +9347,11 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9408,19 +9402,19 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>75</v>
@@ -9428,16 +9422,18 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F79" t="s" s="2">
         <v>81</v>
       </c>
@@ -9454,11 +9450,11 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9485,13 +9481,11 @@
         <v>75</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -9509,7 +9503,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9521,7 +9515,7 @@
         <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>75</v>
@@ -9529,17 +9523,17 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>81</v>
@@ -9557,11 +9551,11 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9588,11 +9582,13 @@
         <v>75</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>75</v>
@@ -9610,7 +9606,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9630,17 +9626,17 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>81</v>
@@ -9658,11 +9654,11 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9713,7 +9709,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -9733,20 +9729,20 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F82" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>76</v>
@@ -9761,11 +9757,11 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9774,7 +9770,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>75</v>
@@ -9816,7 +9812,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -9836,17 +9832,17 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>76</v>
@@ -9864,11 +9860,11 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9877,7 +9873,7 @@
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>75</v>
@@ -9919,7 +9915,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -9939,23 +9935,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E84" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>75</v>
@@ -9967,11 +9961,11 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10022,13 +10016,13 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>75</v>
@@ -10042,10 +10036,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10056,7 +10050,7 @@
         <v>81</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>75</v>
@@ -10068,16 +10062,14 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>75</v>
+        <v>271</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
@@ -10099,13 +10091,11 @@
         <v>75</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>75</v>
@@ -10123,13 +10113,13 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>126</v>
+        <v>273</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>75</v>
@@ -10143,10 +10133,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10169,18 +10159,18 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>75</v>
@@ -10198,11 +10188,13 @@
         <v>75</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>272</v>
+        <v>75</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>75</v>
@@ -10220,7 +10212,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -10240,10 +10232,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10266,7 +10258,7 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>108</v>
+        <v>280</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10277,7 +10269,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>75</v>
@@ -10319,7 +10311,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -10339,10 +10331,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10365,7 +10357,7 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
@@ -10418,7 +10410,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10438,10 +10430,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10464,9 +10456,11 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L89" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -10517,7 +10511,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -10537,10 +10531,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10563,11 +10557,9 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10618,7 +10610,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -10638,10 +10630,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10664,7 +10656,7 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -10717,7 +10709,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -10737,10 +10729,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10763,7 +10755,7 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
@@ -10816,7 +10808,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -10836,10 +10828,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10862,7 +10854,7 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10915,7 +10907,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -10935,10 +10927,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10961,7 +10953,7 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
@@ -11014,7 +11006,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -11034,10 +11026,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11060,7 +11052,7 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11113,7 +11105,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -11133,10 +11125,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11147,7 +11139,7 @@
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>75</v>
@@ -11159,12 +11151,16 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L96" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>342</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>75</v>
       </c>
@@ -11212,13 +11208,13 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>75</v>
@@ -11232,21 +11228,23 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E97" s="2"/>
+      <c r="E97" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>75</v>
@@ -11258,16 +11256,14 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="M97" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L97" s="2"/>
+      <c r="M97" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N97" s="2"/>
-      <c r="O97" t="s" s="2">
-        <v>344</v>
-      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>75</v>
       </c>
@@ -11291,13 +11287,11 @@
         <v>75</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>75</v>
@@ -11315,13 +11309,13 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>341</v>
+        <v>90</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>75</v>
@@ -11335,23 +11329,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E98" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>75</v>
@@ -11363,11 +11355,11 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11394,11 +11386,13 @@
         <v>75</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>75</v>
@@ -11416,13 +11410,13 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>75</v>
@@ -11436,10 +11430,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11450,7 +11444,7 @@
         <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>75</v>
@@ -11462,11 +11456,11 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11517,19 +11511,19 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>75</v>
@@ -11537,16 +11531,18 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F100" t="s" s="2">
         <v>81</v>
       </c>
@@ -11563,11 +11559,11 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11594,13 +11590,11 @@
         <v>75</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y100" s="2"/>
       <c r="Z100" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -11618,7 +11612,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -11630,7 +11624,7 @@
         <v>75</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>75</v>
@@ -11638,17 +11632,17 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>81</v>
@@ -11666,11 +11660,11 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11697,11 +11691,13 @@
         <v>75</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y101" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z101" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>75</v>
@@ -11719,7 +11715,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -11739,17 +11735,17 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>81</v>
@@ -11767,11 +11763,11 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11822,7 +11818,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -11842,20 +11838,20 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>76</v>
@@ -11870,11 +11866,11 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -11883,7 +11879,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>75</v>
@@ -11925,7 +11921,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -11945,17 +11941,17 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>76</v>
@@ -11973,11 +11969,11 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -11986,7 +11982,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>75</v>
@@ -12028,7 +12024,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12048,23 +12044,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E105" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>75</v>
@@ -12076,11 +12070,11 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12131,13 +12125,13 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>75</v>
@@ -12151,10 +12145,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12165,7 +12159,7 @@
         <v>81</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>75</v>
@@ -12177,11 +12171,11 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>123</v>
+        <v>353</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12190,7 +12184,7 @@
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>75</v>
+        <v>271</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>75</v>
@@ -12232,13 +12226,13 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>126</v>
+        <v>352</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>75</v>
@@ -12278,12 +12272,10 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L107" s="2"/>
-      <c r="M107" t="s" s="2">
-        <v>355</v>
-      </c>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -12291,7 +12283,7 @@
       </c>
       <c r="Q107" s="2"/>
       <c r="R107" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="S107" t="s" s="2">
         <v>75</v>
@@ -12353,10 +12345,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12364,7 +12356,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>76</v>
@@ -12379,7 +12371,7 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>108</v>
+        <v>356</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -12390,7 +12382,7 @@
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="S108" t="s" s="2">
         <v>75</v>
@@ -12432,10 +12424,10 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG108" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH108" t="s" s="2">
         <v>76</v>
@@ -12450,107 +12442,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="L109" s="2"/>
-      <c r="M109" s="2"/>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK109">
+  <autoFilter ref="A1:AK108">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12560,7 +12453,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI108">
+  <conditionalFormatting sqref="A2:AI107">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-resultats-evenements.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
